--- a/artfynd/A 52009-2019 artfynd.xlsx
+++ b/artfynd/A 52009-2019 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 52009-2019 artfynd.xlsx
+++ b/artfynd/A 52009-2019 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -793,6 +793,348 @@
           <t>Skogsstyrelsens naturvärdesobjekt</t>
         </is>
       </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>125618887</v>
+      </c>
+      <c r="B3" t="n">
+        <v>56939</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>100038</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Skogsduva</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Columba oenas</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Tjurfällan, Bockholmssättra, Srm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>649249</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6573276</v>
+      </c>
+      <c r="S3" t="n">
+        <v>150</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Salem</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Salem</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-05-29</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-05-29</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Johan Almqvist</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Johan Almqvist</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>125618140</v>
+      </c>
+      <c r="B4" t="n">
+        <v>56949</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100065</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Trana</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Grus grus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Tjurfällan, Bockholmssättra, Srm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>649249</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6573276</v>
+      </c>
+      <c r="S4" t="n">
+        <v>150</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Salem</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Salem</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-05-29</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-05-29</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Johan Almqvist</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Johan Almqvist</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>125618883</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57629</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>102977</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Gröngöling</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Picus viridis</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Tjurfällan, Bockholmssättra, Srm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>649249</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6573276</v>
+      </c>
+      <c r="S5" t="n">
+        <v>150</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Salem</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Salem</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-05-29</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-05-29</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Johan Almqvist</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Johan Almqvist</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 52009-2019 artfynd.xlsx
+++ b/artfynd/A 52009-2019 artfynd.xlsx
@@ -910,10 +910,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125618140</v>
+        <v>125618883</v>
       </c>
       <c r="B4" t="n">
-        <v>56949</v>
+        <v>57629</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -926,21 +926,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100065</v>
+        <v>102977</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Trana</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Grus grus</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -952,7 +952,7 @@
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -1024,10 +1024,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125618883</v>
+        <v>125618149</v>
       </c>
       <c r="B5" t="n">
-        <v>57629</v>
+        <v>56949</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1040,21 +1040,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102977</v>
+        <v>100065</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Trana</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Grus grus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1062,11 +1062,15 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>pulli</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>pulli/nyligen flygga ungar</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>

--- a/artfynd/A 52009-2019 artfynd.xlsx
+++ b/artfynd/A 52009-2019 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>125618887</v>
       </c>
       <c r="B3" t="n">
-        <v>56947</v>
+        <v>56948</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>125618883</v>
       </c>
       <c r="B4" t="n">
-        <v>57645</v>
+        <v>57646</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1017,7 +1017,7 @@
         <v>125618140</v>
       </c>
       <c r="B5" t="n">
-        <v>56958</v>
+        <v>56959</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
